--- a/output/cityscapes_analysis/guishan_cityscapes_results.xlsx
+++ b/output/cityscapes_analysis/guishan_cityscapes_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB37"/>
+  <dimension ref="A1:BD37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,255 +434,265 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>model_type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>hsv_GVI</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>hsv_sky_ratio</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>hsv_sea_ratio</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>hsv_building_ratio</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>hsv_road_ratio</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>hsv_brightness</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hsv_saturation</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>hsv_color_richness</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>hsv_warm_ratio</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>hsv_cool_ratio</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>hsv_enclosure</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>hsv_openness</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>hsv_edge_density</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>hsv_texture</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>hsv_contrast</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>hsv_color_temp</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>coco_background</t>
-        </is>
-      </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>coco_aeroplane</t>
+          <t>seg_background</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>coco_bicycle</t>
+          <t>seg_aeroplane</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>coco_bird</t>
+          <t>seg_bicycle</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>coco_boat</t>
+          <t>seg_bird</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>coco_bottle</t>
+          <t>seg_boat</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>coco_bus</t>
+          <t>seg_bottle</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>coco_car</t>
+          <t>seg_bus</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>coco_cat</t>
+          <t>seg_car</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>coco_chair</t>
+          <t>seg_cat</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>coco_cow</t>
+          <t>seg_chair</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>coco_diningtable</t>
+          <t>seg_cow</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>coco_dog</t>
+          <t>seg_diningtable</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>coco_horse</t>
+          <t>seg_dog</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>coco_motorbike</t>
+          <t>seg_horse</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>coco_person</t>
+          <t>seg_motorbike</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>coco_pottedplant</t>
+          <t>seg_person</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>coco_sheep</t>
+          <t>seg_pottedplant</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>coco_sofa</t>
+          <t>seg_sheep</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>coco_train</t>
+          <t>seg_sofa</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>coco_tvmonitor</t>
+          <t>seg_train</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
+          <t>seg_tvmonitor</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
           <t>scene_hsv_sky</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>scene_hsv_sea</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>scene_hsv_green</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>scene_hsv_building</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>scene_hsv_road</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>scene_hsv_other</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>coco_vehicle_total</t>
-        </is>
-      </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>coco_people_total</t>
+          <t>seg_vehicle_total</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>coco_veg_total</t>
+          <t>seg_people_total</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>coco_boat_total</t>
+          <t>seg_veg_total</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
+          <t>seg_road_total</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>seg_built_total</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
           <t>scene_natural_ratio</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>scene_built_ratio</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>scene_natural_built_ratio</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>scene_urban_intensity</t>
         </is>
@@ -704,60 +714,62 @@
           <t>地图.jpg</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>0.3124590922026181</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07409469265793966</v>
+        <v>0.312834259647651</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01183524829254411</v>
+        <v>0.0745425230704698</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02649624715424018</v>
+        <v>0.01226405201342282</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002761720973249858</v>
+        <v>0.03210072357382551</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7941698106035243</v>
+        <v>0.00278680788590604</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3933579564794045</v>
+        <v>0.7939882457806948</v>
       </c>
       <c r="K2" t="n">
-        <v>0.193095220524755</v>
+        <v>0.3898465824039347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06673618027888446</v>
+        <v>0.1929376205104889</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5538809049516221</v>
+        <v>0.0671743917785235</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3385869913204326</v>
+        <v>0.5545865666946309</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3983890331531019</v>
+        <v>0.3417850776006711</v>
       </c>
       <c r="P2" t="n">
-        <v>0.08306017003414912</v>
+        <v>0.3996408347315436</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7982436311852366</v>
+        <v>0.09821334941275167</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2526909922656753</v>
+        <v>0.7329544490370704</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1204881034788696</v>
+        <v>0.2281513713641115</v>
       </c>
       <c r="T2" t="n">
+        <v>0.1211249508871722</v>
+      </c>
+      <c r="U2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
@@ -816,25 +828,25 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.07409469265793966</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.01183524829254411</v>
+        <v>0.0745425230704698</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.3124590922026181</v>
+        <v>0.01226405201342282</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.01911950412635174</v>
+        <v>0.312834259647651</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.002761720973249858</v>
+        <v>0.02265100671140939</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.5846235593340922</v>
+        <v>0.00278680788590604</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>0.580363884228188</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -846,16 +858,22 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.3983890331531019</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.0218812250996016</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>18.20605680362712</v>
+        <v>0.3996408347315437</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.0218812250996016</v>
+        <v>0.02543781459731544</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>15.70988432667448</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.02543781459731544</v>
       </c>
     </row>
     <row r="3">
@@ -874,59 +892,61 @@
           <t>外围\一环路01.jpg</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>0.04750695248199589</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>0.2597981519659851</v>
+        <v>0.05216725667317709</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01800411522633745</v>
+        <v>0.2568028767903646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3696184825504758</v>
+        <v>0.01808039347330729</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2839492358297968</v>
+        <v>0.3936793009440104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4161844689861622</v>
+        <v>0.3112157185872396</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1798108746908695</v>
+        <v>0.4161525850981668</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1805359172978843</v>
+        <v>0.1666979272381153</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04922566982944316</v>
+        <v>0.1800348827218839</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5864292976787552</v>
+        <v>0.04834620157877604</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5603100686406893</v>
+        <v>0.5984077453613281</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3253092196743184</v>
+        <v>0.574413553873698</v>
       </c>
       <c r="P3" t="n">
-        <v>0.155081729339474</v>
+        <v>0.3270505269368489</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6297779230846903</v>
+        <v>0.1605885823567708</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5467527876996769</v>
+        <v>0.7477056748845305</v>
       </c>
       <c r="S3" t="n">
-        <v>0.083941211810323</v>
+        <v>0.5345654377923733</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9999103546142578</v>
+        <v>0.08079126843238876</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.9975910186767578</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -944,10 +964,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.96453857421875e-05</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.002408981323242188</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -986,28 +1006,28 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2597981519659851</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.01800411522633745</v>
+        <v>0.2568028767903646</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.04750695248199589</v>
+        <v>0.01808039347330729</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.3353671478145898</v>
+        <v>0.05216725667317709</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.2839492358297968</v>
+        <v>0.3602256774902344</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.2797250002009388</v>
+        <v>0.3112157185872396</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.96453857421875e-05</v>
+        <v>0.246667226155599</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.002408981323242188</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -1016,16 +1036,22 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.3253092196743184</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.6193163836443866</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.5252706096509503</v>
+        <v>0.3270505269368489</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.6194060290301288</v>
+        <v>0.6714413960774739</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.4870865004168018</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.6738503774007161</v>
       </c>
     </row>
     <row r="4">
@@ -1044,59 +1070,61 @@
           <t>外围\一环路02.jpg</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>0.2861798447346001</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>0.2135241473162616</v>
+        <v>0.2894236246744792</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02528513213734568</v>
+        <v>0.212774912516276</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4204739543145576</v>
+        <v>0.02544403076171875</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1804018373842593</v>
+        <v>0.4326909383138021</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4923946206086601</v>
+        <v>0.1829071044921875</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1569950470362238</v>
+        <v>0.4923626369900174</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2168808310122129</v>
+        <v>0.1533983367720461</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05690969459313915</v>
+        <v>0.2163693713812467</v>
       </c>
       <c r="M4" t="n">
-        <v>0.127413086439847</v>
+        <v>0.05640792846679688</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5523435741785623</v>
+        <v>0.1282552083333333</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5249891241882073</v>
+        <v>0.5591748555501301</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06023014523855453</v>
+        <v>0.527642567952474</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4921876414109315</v>
+        <v>0.1600990295410156</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4952739279198534</v>
+        <v>0.7461984191118655</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4466515138418905</v>
+        <v>0.4871114003709078</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9944896697998047</v>
+        <v>0.439806612091593</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.9936313629150391</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1114,10 +1142,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.005245208740234375</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>0.006185531616210938</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1138,10 +1166,10 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0002651214599609375</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>0.00018310546875</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1156,46 +1184,52 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.2135241473162616</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.02528513213734568</v>
+        <v>0.212774912516276</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.2861798447346001</v>
+        <v>0.02544403076171875</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.3099784694090792</v>
+        <v>0.2894236246744792</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.1804018373842593</v>
+        <v>0.3181788126627604</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.1194049222969714</v>
+        <v>0.1829071044921875</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.005245208740234375</v>
+        <v>0.1079750061035156</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0002651214599609375</v>
+        <v>0.006185531616210938</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>0.00018310546875</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.5249891241882073</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.4903803067933384</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.070573280252409</v>
+        <v>0.527642567952474</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.4958906369935338</v>
+        <v>0.501085917154948</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.052996096861404</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.5074545542399089</v>
       </c>
     </row>
     <row r="5">
@@ -1214,59 +1248,61 @@
           <t>外围\一环路03.jpg</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>0.03494281533323688</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>0.2115440839602623</v>
+        <v>0.03430302937825521</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0809740608121142</v>
+        <v>0.2111422220865885</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4510637448157793</v>
+        <v>0.08344523111979167</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2511267014491705</v>
+        <v>0.4575983683268229</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5371271474938757</v>
+        <v>0.2536176045735677</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1410073990684478</v>
+        <v>0.5370825624154284</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1518814143754509</v>
+        <v>0.1397125792659186</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06313264320907279</v>
+        <v>0.1514255365808968</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5365736847551762</v>
+        <v>0.06319936116536458</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6213408670307677</v>
+        <v>0.5374565124511719</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3274609601056134</v>
+        <v>0.625469970703125</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02342129931037809</v>
+        <v>0.3288904825846354</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4261274726836521</v>
+        <v>0.07020950317382812</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4716167552103713</v>
+        <v>0.6742389921777203</v>
       </c>
       <c r="S5" t="n">
-        <v>0.117658631692396</v>
+        <v>0.4671852140601045</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9774894714355469</v>
+        <v>0.117589501869892</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.9749164581298828</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1281,13 +1317,13 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002338409423828125</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.008623123168945312</v>
+        <v>0.01604843139648438</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>0.001415252685546875</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1305,13 +1341,13 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.01058769226074219</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0009613037109375</v>
+        <v>0.006650924682617188</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>0.00096893310546875</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
@@ -1326,46 +1362,52 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.2115440839602623</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0809740608121142</v>
+        <v>0.2111422220865885</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.03494281533323688</v>
+        <v>0.08344523111979167</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.3475317307460455</v>
+        <v>0.03430302937825521</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.2511267014491705</v>
+        <v>0.3520062764485677</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.3111302254131301</v>
+        <v>0.2536176045735677</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.02154922485351562</v>
+        <v>0.3053741455078125</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0009613037109375</v>
+        <v>0.02411460876464844</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>0.00096893310546875</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.3274609601056134</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.5986584321952161</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.5469903963675161</v>
+        <v>0.3288904825846354</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.6211689607596692</v>
+        <v>0.6056238810221354</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.5430597270534111</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.6307074228922526</v>
       </c>
     </row>
     <row r="6">
@@ -1384,59 +1426,61 @@
           <t>外围\九洲栈道.jpg</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>0.3059448744534465</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>0.06230797787262089</v>
+        <v>0.30975341796875</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06036062986271862</v>
+        <v>0.06163533528645834</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2560075045613104</v>
+        <v>0.06012852986653646</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08383549191824202</v>
+        <v>0.2586491902669271</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4255889183382409</v>
+        <v>0.08336512247721355</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3157225291857677</v>
+        <v>0.42556368759255</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2388755250266376</v>
+        <v>0.3119153091330933</v>
       </c>
       <c r="L6" t="n">
-        <v>0.363027501989294</v>
+        <v>0.2382130742702333</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1438629401564107</v>
+        <v>0.363616943359375</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4799539322715728</v>
+        <v>0.1438382466634115</v>
       </c>
       <c r="O6" t="n">
-        <v>0.428613482188786</v>
+        <v>0.4809117635091146</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03908259387860082</v>
+        <v>0.4315172831217448</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5011674554322765</v>
+        <v>0.1251881917317708</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5100448507308494</v>
+        <v>0.7585992728465085</v>
       </c>
       <c r="S6" t="n">
-        <v>2.523408587270763</v>
+        <v>0.5013943529315076</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2.527939709043739</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.9997005462646484</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1463,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>0.0002994537353515625</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1496,25 +1540,25 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.06230797787262089</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.06036062986271862</v>
+        <v>0.06163533528645834</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.3059448744534465</v>
+        <v>0.06012852986653646</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1283124758873457</v>
+        <v>0.30975341796875</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.08383549191824202</v>
+        <v>0.1296984354654948</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.4436474081910687</v>
+        <v>0.08336512247721355</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>0.4398333231608073</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -1526,16 +1570,22 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.428613482188786</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.2121479678055877</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.020342057857973</v>
+        <v>0.4315172831217448</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.2121479678055877</v>
+        <v>0.2130635579427083</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.025288895010765</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.2130635579427083</v>
       </c>
     </row>
     <row r="7">
@@ -1554,68 +1604,70 @@
           <t>外围\九洲栈道方向步行绿道01.jpg</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>0.3622110625843943</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>0.03066319595148534</v>
+        <v>0.3636347452799479</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00537366827819573</v>
+        <v>0.02888743082682292</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1368010093155221</v>
+        <v>0.005331675211588542</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1163793493200232</v>
+        <v>0.144659678141276</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3669013786823806</v>
+        <v>0.1203689575195312</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3217735488141775</v>
+        <v>0.3668804841883042</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1875499557776706</v>
+        <v>0.3172211491204555</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3315961547349215</v>
+        <v>0.1857864929658077</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09291936929333848</v>
+        <v>0.3319320678710938</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4035057538821374</v>
+        <v>0.09261322021484375</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3982479268140753</v>
+        <v>0.4082913716634115</v>
       </c>
       <c r="P7" t="n">
-        <v>0.07240609377009388</v>
+        <v>0.3978538513183594</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.526425379103621</v>
+        <v>0.1996714274088542</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5240468946407622</v>
+        <v>0.7845077798311708</v>
       </c>
       <c r="S7" t="n">
-        <v>3.568605648650752</v>
+        <v>0.5134346393665832</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9999942779541016</v>
+        <v>3.584029181491649</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.9999790191650391</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>5.7220458984375e-06</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.09808349609375e-05</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1666,25 +1718,25 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.03066319595148534</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.00537366827819573</v>
+        <v>0.02888743082682292</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.3622110625843943</v>
+        <v>0.005331675211588542</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.1092913592303241</v>
+        <v>0.3636347452799479</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.1163793493200232</v>
+        <v>0.1155878702799479</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.4381264266653807</v>
+        <v>0.1203689575195312</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>0.4331067403157552</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -1696,16 +1748,22 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.3982479268140754</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.2256707085503472</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.764722434071644</v>
+        <v>0.3978538513183594</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.2256707085503472</v>
+        <v>0.2359568277994792</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.686122706878206</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.2359568277994792</v>
       </c>
     </row>
     <row r="8">
@@ -1724,60 +1782,62 @@
           <t>外围\九洲栈道方向步行绿道02.jpg</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0.3005321486987204</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0.2716004171489197</v>
+        <v>0.3043479919433594</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03632791150253987</v>
+        <v>0.2714958190917969</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1648685157053755</v>
+        <v>0.04080708821614584</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1806769351409787</v>
+        <v>0.1731923421223958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4745919016980667</v>
+        <v>0.1822764078776042</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2562850667731406</v>
+        <v>0.4745454775741677</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1846570250112513</v>
+        <v>0.248745039397595</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1056911013253922</v>
+        <v>0.1840436156936346</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1373882529176312</v>
+        <v>0.1060981750488281</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3844945962536973</v>
+        <v>0.1379254659016927</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6084604773501801</v>
+        <v>0.3887466430664063</v>
       </c>
       <c r="P8" t="n">
-        <v>0.06344020513840663</v>
+        <v>0.616650899251302</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5621582100927178</v>
+        <v>0.1525472005208333</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5592277059381492</v>
+        <v>0.7940576716836414</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7692821605832378</v>
+        <v>0.5476087742882196</v>
       </c>
       <c r="T8" t="n">
+        <v>0.7692372479437685</v>
+      </c>
+      <c r="U8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
@@ -1836,25 +1896,25 @@
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.2716004171489197</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.03632791150253987</v>
+        <v>0.2714958190917969</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.3005321486987204</v>
+        <v>0.04080708821614584</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.1464788491833848</v>
+        <v>0.3043479919433594</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.1806769351409787</v>
+        <v>0.1517308553059896</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.1578868975855195</v>
+        <v>0.1822764078776042</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>0.1456146240234375</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -1866,16 +1926,22 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.6084604773501801</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.3271557843243634</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.859843678946651</v>
+        <v>0.6166508992513021</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.3271557843243634</v>
+        <v>0.3340072631835938</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.846214501921914</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.3340072631835938</v>
       </c>
     </row>
     <row r="9">
@@ -1894,60 +1960,62 @@
           <t>外围\九洲栈道方向步行绿道03.jpg</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>0.2462496659392683</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E9" t="n">
-        <v>0.2145379462850437</v>
+        <v>0.2477060953776042</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03274014947836291</v>
+        <v>0.2138226826985677</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3017323811848958</v>
+        <v>0.03428777058919271</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09891896188994985</v>
+        <v>0.3081156412760417</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4942437846580006</v>
+        <v>0.1011784871419271</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2297157769629119</v>
+        <v>0.4941842072929432</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2088628981172826</v>
+        <v>0.2258039437088312</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2019760696976273</v>
+        <v>0.2084531165180726</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1763340200416345</v>
+        <v>0.2028986612955729</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4888819062660751</v>
+        <v>0.1765963236490885</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4935277617026749</v>
+        <v>0.4925636291503906</v>
       </c>
       <c r="P9" t="n">
-        <v>0.06009652094585905</v>
+        <v>0.4958165486653646</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4563434873326495</v>
+        <v>0.1787796020507812</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4542482309087613</v>
+        <v>0.7398434993580555</v>
       </c>
       <c r="S9" t="n">
-        <v>1.145410988979606</v>
+        <v>0.4465272858074728</v>
       </c>
       <c r="T9" t="n">
+        <v>1.148933953827902</v>
+      </c>
+      <c r="U9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
@@ -2006,25 +2074,25 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.2145379462850437</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.03274014947836291</v>
+        <v>0.2138226826985677</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.2462496659392683</v>
+        <v>0.03428777058919271</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.2482031049061214</v>
+        <v>0.2477060953776042</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.09891896188994985</v>
+        <v>0.2534395853678386</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.2395382476932227</v>
+        <v>0.1011784871419271</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>0.2320721944173177</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -2036,16 +2104,22 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.4935277617026749</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.3471220667960713</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.42176596403665</v>
+        <v>0.4958165486653646</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.3471220667960713</v>
+        <v>0.3546180725097656</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.398166616240616</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.3546180725097656</v>
       </c>
     </row>
     <row r="10">
@@ -2064,60 +2138,62 @@
           <t>外围\妈祖庙.jpg</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>0.03267660258728781</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E10" t="n">
-        <v>0.2452715336050026</v>
+        <v>0.03329594930013021</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02141957224151235</v>
+        <v>0.2438926696777344</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2522656476056134</v>
+        <v>0.0218658447265625</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2158634515456211</v>
+        <v>0.2637952168782552</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4372401708822836</v>
+        <v>0.2260487874348958</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2281217477958985</v>
+        <v>0.4371750725640191</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2845551263153199</v>
+        <v>0.2218986311769174</v>
       </c>
       <c r="L10" t="n">
-        <v>0.381061695240162</v>
+        <v>0.2827120276344368</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1714737503616898</v>
+        <v>0.3828684488932292</v>
       </c>
       <c r="N10" t="n">
-        <v>0.49576976132491</v>
+        <v>0.1694246927897135</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2993677084338027</v>
+        <v>0.5028394063313801</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1036059218669624</v>
+        <v>0.2990544637044271</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5892389092507833</v>
+        <v>0.1424903869628906</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5302880706443827</v>
+        <v>0.7149845240592769</v>
       </c>
       <c r="S10" t="n">
-        <v>2.222261262584682</v>
+        <v>0.5209560519010974</v>
       </c>
       <c r="T10" t="n">
+        <v>2.25980158374465</v>
+      </c>
+      <c r="U10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
@@ -2176,25 +2252,25 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.2452715336050026</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.02141957224151235</v>
+        <v>0.2438926696777344</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.03267660258728781</v>
+        <v>0.0218658447265625</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.2259706724818351</v>
+        <v>0.03329594930013021</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.2158634515456211</v>
+        <v>0.2346267700195312</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.3672798690481932</v>
+        <v>0.2260487874348958</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>0.35467529296875</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -2206,16 +2282,22 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.2993677084338027</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.4418341240274563</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.6775552511646847</v>
+        <v>0.2990544637044271</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.4418341240274563</v>
+        <v>0.4606755574544271</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.6491636243808897</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.4606755574544271</v>
       </c>
     </row>
     <row r="11">
@@ -2234,59 +2316,61 @@
           <t>外围\妈祖庙方向小路01.jpg</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>0.1618210906354488</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E11" t="n">
-        <v>0.08494869279272763</v>
+        <v>0.1628430684407552</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04851045333799511</v>
+        <v>0.09144846598307292</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2923614125192901</v>
+        <v>0.04834238688151041</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2068715664584941</v>
+        <v>0.3028399149576823</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4192547419780508</v>
+        <v>0.2080777486165365</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2524021729520319</v>
+        <v>0.4191807815452027</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2729396551721234</v>
+        <v>0.2489964902790543</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3849954487364969</v>
+        <v>0.2719699283987783</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1353499801070602</v>
+        <v>0.3847401936848958</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5260628908259388</v>
+        <v>0.1345634460449219</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2952802367661715</v>
+        <v>0.5308456420898438</v>
       </c>
       <c r="P11" t="n">
-        <v>0.08431724265769676</v>
+        <v>0.3026339213053386</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5510070851323159</v>
+        <v>0.220483144124349</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4346225571767608</v>
+        <v>0.7976479626166597</v>
       </c>
       <c r="S11" t="n">
-        <v>2.844423057978394</v>
+        <v>0.4194520205402091</v>
       </c>
       <c r="T11" t="n">
-        <v>0.999786376953125</v>
+        <v>2.859151915629016</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.9969367980957031</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2298,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>0.003063201904296875</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2310,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.000213623046875</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2346,25 +2430,25 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.08494869279272763</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.04851045333799511</v>
+        <v>0.09144846598307292</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.1618210906354488</v>
+        <v>0.04834238688151041</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.2381353182066615</v>
+        <v>0.1628430684407552</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.2068715664584941</v>
+        <v>0.2436319986979167</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.4037405885296104</v>
+        <v>0.2080777486165365</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>0.3956693013509114</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -2376,16 +2460,22 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.2952802367661715</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.4450068846651556</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.6635393370352393</v>
+        <v>0.3026339213053386</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.4450068846651556</v>
+        <v>0.4517097473144531</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.669972815799894</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.4517097473144531</v>
       </c>
     </row>
     <row r="12">
@@ -2404,59 +2494,61 @@
           <t>外围\妈祖庙方向小路02.jpg</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>0.2649662975421168</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E12" t="n">
-        <v>0.1963149961620692</v>
+        <v>0.2682139078776042</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05544510201662166</v>
+        <v>0.1991055806477865</v>
       </c>
       <c r="G12" t="n">
-        <v>0.194528650354456</v>
+        <v>0.05965423583984375</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05581162692097479</v>
+        <v>0.197851816813151</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4464940151367582</v>
+        <v>0.05526097615559896</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2826342441494505</v>
+        <v>0.4464595620149101</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2319343770729824</v>
+        <v>0.2771470961227915</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2653672332135738</v>
+        <v>0.2316396489635144</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1922997996640304</v>
+        <v>0.2659784952799479</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4244609314718365</v>
+        <v>0.1940167744954427</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5167263957208076</v>
+        <v>0.4252471923828125</v>
       </c>
       <c r="P12" t="n">
-        <v>0.06533198101530349</v>
+        <v>0.5269737243652344</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5319520324357802</v>
+        <v>0.1766204833984375</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5261874048547899</v>
+        <v>0.7775268112449893</v>
       </c>
       <c r="S12" t="n">
-        <v>1.379959072854602</v>
+        <v>0.5162794181775351</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9972019195556641</v>
+        <v>1.370897568388485</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2510,31 +2602,31 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.002798080444335938</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.1963149961620692</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.05544510201662166</v>
+        <v>0.1991055806477865</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.2649662975421168</v>
+        <v>0.05965423583984375</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.1713807533797904</v>
+        <v>0.2682139078776042</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.05581162692097479</v>
+        <v>0.1735038757324219</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.2985604368610146</v>
+        <v>0.05526097615559896</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.002798080444335938</v>
+        <v>0.2896080017089844</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -2546,16 +2638,22 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.5167263957208076</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.2271923803007652</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.274390191460465</v>
+        <v>0.5269737243652344</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.2299904607451011</v>
+        <v>0.2287648518880208</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.30355063929377</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.2287648518880208</v>
       </c>
     </row>
     <row r="13">
@@ -2574,59 +2672,61 @@
           <t>外围\桂海三路.jpg</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>0.1189063429341885</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E13" t="n">
-        <v>0.1476371984913516</v>
+        <v>0.1215159098307292</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02176254963188014</v>
+        <v>0.1473236083984375</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4585801112798997</v>
+        <v>0.02303059895833333</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3031164726602688</v>
+        <v>0.4747543334960938</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4242519039146973</v>
+        <v>0.3087743123372396</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1668575594983685</v>
+        <v>0.4241990282644634</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2407762132328583</v>
+        <v>0.1635832643197253</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2050541379324203</v>
+        <v>0.2397488634427726</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2111973389676569</v>
+        <v>0.2039922078450521</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6218393584828318</v>
+        <v>0.2103805541992188</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2883060910574203</v>
+        <v>0.6310846964518229</v>
       </c>
       <c r="P13" t="n">
-        <v>0.04624009622958462</v>
+        <v>0.2918701171875</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5116747455812649</v>
+        <v>0.14715576171875</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4901953489373398</v>
+        <v>0.7663227755851464</v>
       </c>
       <c r="S13" t="n">
-        <v>0.970907910236086</v>
+        <v>0.4795372598901125</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9672927856445312</v>
+        <v>0.9696297216812253</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.965576171875</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2641,13 +2741,13 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.03164863586425781</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.001058578491210938</v>
+        <v>0.03374671936035156</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>0.0006771087646484375</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2686,28 +2786,28 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.1476371984913516</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.02176254963188014</v>
+        <v>0.1473236083984375</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.1189063429341885</v>
+        <v>0.02303059895833333</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.4102391372492284</v>
+        <v>0.1215159098307292</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.3031164726602688</v>
+        <v>0.4249089558919271</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.2408491848918146</v>
+        <v>0.3087743123372396</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.03270721435546875</v>
+        <v>0.2248509724934896</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>0.034423828125</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -2716,16 +2816,22 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.2883060910574203</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.7133556099094971</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.4041542295290393</v>
+        <v>0.2918701171875</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.7460628242649658</v>
+        <v>0.7336832682291666</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.3978143321676542</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.7681070963541666</v>
       </c>
     </row>
     <row r="14">
@@ -2744,65 +2850,67 @@
           <t>外围\桂海二路01.jpg</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>0.01514601216885288</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E14" t="n">
-        <v>0.2261835420082626</v>
+        <v>0.01501719156901042</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04854951081452547</v>
+        <v>0.2263895670572917</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3553758786048418</v>
+        <v>0.04836273193359375</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2454665698141718</v>
+        <v>0.3680877685546875</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5121934129685262</v>
+        <v>0.2480901082356771</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1857167736685402</v>
+        <v>0.5121018752553104</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2382276939478178</v>
+        <v>0.1821682350308287</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1977545969770769</v>
+        <v>0.2368693405530625</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3821673609101723</v>
+        <v>0.197021484375</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5649596163274819</v>
+        <v>0.3817723592122396</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2898790649916409</v>
+        <v>0.5725713094075522</v>
       </c>
       <c r="P14" t="n">
-        <v>0.05558444050604424</v>
+        <v>0.2897694905598958</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5404440011687323</v>
+        <v>0.1418774922688802</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5170393316373785</v>
+        <v>0.7822854224687601</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5174541307032965</v>
+        <v>0.505306513932326</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9761714935302734</v>
+        <v>0.5160692322312351</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.9605312347412109</v>
       </c>
       <c r="V14" t="n">
-        <v>0.01947021484375</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.01094627380371094</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2814,10 +2922,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0002536773681640625</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>0.01074409484863281</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2835,13 +2943,13 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.002706527709960938</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.001398086547851562</v>
+        <v>0.01651382446289062</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>0.001264572143554688</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2856,46 +2964,52 @@
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.2261835420082626</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.04854951081452547</v>
+        <v>0.2263895670572917</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.01514601216885288</v>
+        <v>0.04836273193359375</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.2994242224673676</v>
+        <v>0.01501719156901042</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.2454665698141718</v>
+        <v>0.3086891174316406</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.3534284678015689</v>
+        <v>0.2480901082356771</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.022430419921875</v>
+        <v>0.3439572652180989</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.001398086547851562</v>
+        <v>0.03820419311523438</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>0.001264572143554688</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.289879064991641</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.5448907922815394</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.5319938180347259</v>
+        <v>0.2897694905598958</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.5687192987512659</v>
+        <v>0.5567792256673177</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.5204378266354528</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.5962479909261068</v>
       </c>
     </row>
     <row r="15">
@@ -2914,59 +3028,61 @@
           <t>外围\桂海二路02.jpg</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>0.05188779477719908</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E15" t="n">
-        <v>0.147784323358732</v>
+        <v>0.05284881591796875</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02417431741094393</v>
+        <v>0.1501515706380208</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3253329555684156</v>
+        <v>0.02403386433919271</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1846152097599987</v>
+        <v>0.3382059733072917</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4930437102633701</v>
+        <v>0.1886405944824219</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2435538657687146</v>
+        <v>0.4929579840766059</v>
       </c>
       <c r="K15" t="n">
-        <v>0.243953786514248</v>
+        <v>0.2394125396130132</v>
       </c>
       <c r="L15" t="n">
-        <v>0.332648006486304</v>
+        <v>0.2428582156782612</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2964405326686279</v>
+        <v>0.3326301574707031</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5552653497138632</v>
+        <v>0.2968940734863281</v>
       </c>
       <c r="O15" t="n">
-        <v>0.223846435546875</v>
+        <v>0.5623235066731771</v>
       </c>
       <c r="P15" t="n">
-        <v>0.04675920902456276</v>
+        <v>0.2270342508951823</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.5379297606923441</v>
+        <v>0.1391677856445312</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4961354489475883</v>
+        <v>0.775528287151199</v>
       </c>
       <c r="S15" t="n">
-        <v>1.122136980914037</v>
+        <v>0.4829043719760257</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9952831268310547</v>
+        <v>1.120362670773722</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.9959430694580078</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2984,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.003458023071289062</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>0.002721786499023438</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3008,10 +3124,10 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.00125885009765625</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>0.00133514404296875</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -3026,46 +3142,52 @@
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.147784323358732</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.02417431741094393</v>
+        <v>0.1501515706380208</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.05188779477719908</v>
+        <v>0.02403386433919271</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.2878424876020769</v>
+        <v>0.05284881591796875</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.1846152097599987</v>
+        <v>0.2979087829589844</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.4303395463605967</v>
+        <v>0.1886405944824219</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.003458023071289062</v>
+        <v>0.4172045389811198</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.00125885009765625</v>
+        <v>0.002721786499023438</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>0.00133514404296875</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.223846435546875</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.4724576973620757</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.4737904853835868</v>
+        <v>0.2270342508951823</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.477174570531021</v>
+        <v>0.4865493774414062</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.466620233836985</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.4906063079833984</v>
       </c>
     </row>
     <row r="16">
@@ -3084,60 +3206,62 @@
           <t>外围\桂海二路03.jpg</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>0.1173370110154642</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E16" t="n">
-        <v>0.0551165671014982</v>
+        <v>0.1182352701822917</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0111370950078768</v>
+        <v>0.05516306559244791</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2809857027030285</v>
+        <v>0.01230748494466146</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2484826609921554</v>
+        <v>0.2921765645345052</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5531500801647257</v>
+        <v>0.2489814758300781</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2200305456997051</v>
+        <v>0.5530587888231464</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2787981382800157</v>
+        <v>0.2158395355822993</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2141489413540059</v>
+        <v>0.2776272567534152</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1436351886011445</v>
+        <v>0.2124188741048177</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5341007059984246</v>
+        <v>0.1429494222005208</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1835906731248392</v>
+        <v>0.5406262715657553</v>
       </c>
       <c r="P16" t="n">
-        <v>0.06537392698688271</v>
+        <v>0.1857058207194011</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5523469973584849</v>
+        <v>0.1578992207845052</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5463456080112989</v>
+        <v>0.7872290511862869</v>
       </c>
       <c r="S16" t="n">
-        <v>1.490912168023786</v>
+        <v>0.5340537596520563</v>
       </c>
       <c r="T16" t="n">
+        <v>1.485961851912906</v>
+      </c>
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
@@ -3196,25 +3320,25 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.0551165671014982</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0111370950078768</v>
+        <v>0.05516306559244791</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.1173370110154642</v>
+        <v>0.01230748494466146</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.2626180138607574</v>
+        <v>0.1182352701822917</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.2484826609921554</v>
+        <v>0.2710202534993489</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.478989400981385</v>
+        <v>0.2489814758300781</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>0.469696044921875</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -3226,16 +3350,22 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.1835906731248392</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.5111006748529128</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.3592057748151066</v>
+        <v>0.1857058207194011</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.5111006748529128</v>
+        <v>0.520001729329427</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.3571247038623802</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.520001729329427</v>
       </c>
     </row>
     <row r="17">
@@ -3254,60 +3384,62 @@
           <t>外围\步行绿道望海方向.jpg</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>0.2512231520664545</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E17" t="n">
-        <v>0.3344216052396798</v>
+        <v>0.2567545572916667</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0134612032415445</v>
+        <v>0.3336613972981771</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2338101108378344</v>
+        <v>0.01410039265950521</v>
       </c>
       <c r="H17" t="n">
-        <v>0.06928965878584747</v>
+        <v>0.2371355692545573</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5526763869228408</v>
+        <v>0.07391611735026042</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2111917121891516</v>
+        <v>0.5526314180660871</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1493983597494304</v>
+        <v>0.2062105066636029</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02063365041473765</v>
+        <v>0.1489965033027289</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2672507203655479</v>
+        <v>0.02058792114257812</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4231571150414738</v>
+        <v>0.2689221700032552</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5991059605476787</v>
+        <v>0.4241981506347656</v>
       </c>
       <c r="P17" t="n">
-        <v>0.05020625110516332</v>
+        <v>0.6045163472493489</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4316801829447338</v>
+        <v>0.1450576782226562</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4774625972017164</v>
+        <v>0.6914443943470783</v>
       </c>
       <c r="S17" t="n">
-        <v>0.07720680108818335</v>
+        <v>0.4727860983962159</v>
       </c>
       <c r="T17" t="n">
+        <v>0.07655688850584692</v>
+      </c>
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
@@ -3366,25 +3498,25 @@
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.3344216052396798</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.0134612032415445</v>
+        <v>0.3336613972981771</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.2512231520664545</v>
+        <v>0.01410039265950521</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.2022141193656764</v>
+        <v>0.2567545572916667</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.06928965878584747</v>
+        <v>0.2045440673828125</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.1841106650270062</v>
+        <v>0.07391611735026042</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>0.1760037740071615</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -3396,16 +3528,22 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.5991059605476788</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.2715037781515239</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.206612954020736</v>
+        <v>0.604516347249349</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.2715037781515239</v>
+        <v>0.2784601847330729</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.170917816890084</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.2784601847330729</v>
       </c>
     </row>
     <row r="18">
@@ -3424,59 +3562,61 @@
           <t>外围\海景01.jpg</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>0.0494330135392554</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E18" t="n">
-        <v>0.3029560355983154</v>
+        <v>0.051422119140625</v>
       </c>
       <c r="F18" t="n">
-        <v>0.103584760501061</v>
+        <v>0.2976239522298177</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4692220805603781</v>
+        <v>0.1157608032226562</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1631671921215921</v>
+        <v>0.4984639485677083</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5224564333684621</v>
+        <v>0.1685498555501302</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1631766736743083</v>
+        <v>0.5223983764648438</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1541482993617976</v>
+        <v>0.1556667801601435</v>
       </c>
       <c r="L18" t="n">
-        <v>0.077264605235661</v>
+        <v>0.1533345790593962</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6177649478362911</v>
+        <v>0.07703653971354167</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6110554385087127</v>
+        <v>0.6215616861979166</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4559738096386317</v>
+        <v>0.6292691548665365</v>
       </c>
       <c r="P18" t="n">
-        <v>0.06031880947788066</v>
+        <v>0.4648068745930989</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5984867748115708</v>
+        <v>0.1413625081380208</v>
       </c>
       <c r="R18" t="n">
-        <v>0.517650731501438</v>
+        <v>0.829924656867284</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1250710006051292</v>
+        <v>0.4987012276843302</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9704627990722656</v>
+        <v>0.1239400971521831</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.97076416015625</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3485,19 +3625,19 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.02856063842773438</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>0.02722549438476562</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0001010894775390625</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>0.00110626220703125</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3518,10 +3658,10 @@
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.0008754730224609375</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>0.000904083251953125</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3536,46 +3676,52 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.3029560355983154</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.103584760501061</v>
+        <v>0.2976239522298177</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.0494330135392554</v>
+        <v>0.1157608032226562</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.3195925740057549</v>
+        <v>0.051422119140625</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.1631671921215921</v>
+        <v>0.3322995503743489</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.2259738749437371</v>
+        <v>0.1685498555501302</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.0001010894775390625</v>
+        <v>0.2064844767252604</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.0008754730224609375</v>
+        <v>0.00110626220703125</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>0.000904083251953125</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.02856063842773438</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.4559738096386317</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.4827597661273469</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.9445129795786903</v>
+        <v>0.4648068745930989</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.4837363286273469</v>
+        <v>0.5008494059244791</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.9280353356910026</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.5028597513834635</v>
       </c>
     </row>
     <row r="19">
@@ -3594,59 +3740,61 @@
           <t>外围\海景02.jpg</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>0.01364851586612654</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E19" t="n">
-        <v>0.3774297894764339</v>
+        <v>0.01314036051432292</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07361737788949975</v>
+        <v>0.3778775533040364</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4316778614687822</v>
+        <v>0.07779947916666667</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2139960394965278</v>
+        <v>0.4483222961425781</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5598952154958161</v>
+        <v>0.2204640706380208</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1412175468100692</v>
+        <v>0.5598252290214589</v>
       </c>
       <c r="K19" t="n">
-        <v>0.09148554350208266</v>
+        <v>0.1377147948819827</v>
       </c>
       <c r="L19" t="n">
-        <v>0.004100909448945473</v>
+        <v>0.09047526224585091</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6125902717496142</v>
+        <v>0.004039764404296875</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5807910558127573</v>
+        <v>0.6143760681152344</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4646956832320602</v>
+        <v>0.590789794921875</v>
       </c>
       <c r="P19" t="n">
-        <v>0.03447651176295653</v>
+        <v>0.4688173929850261</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.5427065969106375</v>
+        <v>0.09047571818033855</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5347662800792903</v>
+        <v>0.7775513989852143</v>
       </c>
       <c r="S19" t="n">
-        <v>0.006694364804175086</v>
+        <v>0.5247141654742782</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9521617889404297</v>
+        <v>0.006575382796577891</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.9514522552490234</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3655,19 +3803,19 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.02625656127929688</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>0.0263824462890625</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.01918983459472656</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>0.01950454711914062</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3688,10 +3836,10 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.002391815185546875</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>0.002660751342773438</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3706,46 +3854,52 @@
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.3774297894764339</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.07361737788949975</v>
+        <v>0.3778775533040364</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.01364851586612654</v>
+        <v>0.07779947916666667</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.3255523556053884</v>
+        <v>0.01314036051432292</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.2139960394965278</v>
+        <v>0.33612060546875</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.2568854186760545</v>
+        <v>0.2204640706380208</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.01918983459472656</v>
+        <v>0.2422815958658854</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.002391815185546875</v>
+        <v>0.01950454711914062</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>0.002660751342773438</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.02625656127929688</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.4646956832320602</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.5395483951019162</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.8612662481889785</v>
+        <v>0.4688173929850261</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.5611300448821896</v>
+        <v>0.5565846761067709</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.8423094828173262</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0.5787499745686849</v>
       </c>
     </row>
     <row r="20">
@@ -3764,60 +3918,62 @@
           <t>外围\环翠亭.jpg</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>0.3231689076364776</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E20" t="n">
-        <v>0.4664282151210455</v>
+        <v>0.3349838256835938</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0003728670347865227</v>
+        <v>0.46697998046875</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1700900984399113</v>
+        <v>0.0003369649251302083</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0230669563199267</v>
+        <v>0.1641031901041667</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5530574993428119</v>
+        <v>0.0218963623046875</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2250717681439056</v>
+        <v>0.5530355067034952</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1689504983431578</v>
+        <v>0.2170246847314772</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1172210944532858</v>
+        <v>0.1688589134526216</v>
       </c>
       <c r="M20" t="n">
-        <v>0.112003216527617</v>
+        <v>0.118597666422526</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3441346345124421</v>
+        <v>0.1117210388183594</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7899699897923096</v>
+        <v>0.3380691528320313</v>
       </c>
       <c r="P20" t="n">
-        <v>0.08089933670106739</v>
+        <v>0.8023007710774739</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4098037462876424</v>
+        <v>0.1929893493652344</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5463325124269633</v>
+        <v>0.761839709746736</v>
       </c>
       <c r="S20" t="n">
-        <v>1.046577513663357</v>
+        <v>0.5396264492075342</v>
       </c>
       <c r="T20" t="n">
+        <v>1.061542267549783</v>
+      </c>
+      <c r="U20" t="n">
         <v>1</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
@@ -3876,25 +4032,25 @@
         <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.4664282151210455</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.0003728670347865227</v>
+        <v>0.46697998046875</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.3231689076364776</v>
+        <v>0.0003369649251302083</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.07490363729343492</v>
+        <v>0.3349838256835938</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.0230669563199267</v>
+        <v>0.06985219319661458</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.1342855696815522</v>
+        <v>0.0218963623046875</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>0.1270027160644531</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -3906,16 +4062,22 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.7899699897923097</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.09797059361336162</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.063255487196358</v>
+        <v>0.802300771077474</v>
       </c>
       <c r="BB20" t="n">
-        <v>0.09797059361336162</v>
+        <v>0.09174855550130208</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>8.744464937119918</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0.09174855550130208</v>
       </c>
     </row>
     <row r="21">
@@ -3934,59 +4096,61 @@
           <t>外围\环翠亭方向步行绿道01.jpg</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>0.4603351859889404</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E21" t="n">
-        <v>0.1786129170484504</v>
+        <v>0.4647293090820312</v>
       </c>
       <c r="F21" t="n">
-        <v>0.005573037229938272</v>
+        <v>0.1790390014648438</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1043065702964249</v>
+        <v>0.0056304931640625</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01998267154144161</v>
+        <v>0.1073862711588542</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4287707064463999</v>
+        <v>0.01973342895507812</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4130937322504072</v>
+        <v>0.4287511090047998</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1816619453257802</v>
+        <v>0.4061410542407067</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2878855638543274</v>
+        <v>0.181329180543327</v>
       </c>
       <c r="M21" t="n">
-        <v>0.05369046686117541</v>
+        <v>0.2884864807128906</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3347943215703768</v>
+        <v>0.05455907185872396</v>
       </c>
       <c r="O21" t="n">
-        <v>0.644521140267329</v>
+        <v>0.3356781005859375</v>
       </c>
       <c r="P21" t="n">
-        <v>0.07455752023453575</v>
+        <v>0.6493988037109375</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.478482039683771</v>
+        <v>0.1886138916015625</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4953665005713405</v>
+        <v>0.75398725636478</v>
       </c>
       <c r="S21" t="n">
-        <v>5.361849483432515</v>
+        <v>0.4872865280206867</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9999504089355469</v>
+        <v>5.287501846769702</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4010,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.9591064453125e-05</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -4046,25 +4210,25 @@
         <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.1786129170484504</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.005573037229938272</v>
+        <v>0.1790390014648438</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.4603351859889404</v>
+        <v>0.0056304931640625</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.06988833078141075</v>
+        <v>0.4647293090820312</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.01998267154144161</v>
+        <v>0.07229359944661458</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.2826925521034272</v>
+        <v>0.01973342895507812</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>0.2756627400716146</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -4076,16 +4240,22 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.644521140267329</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.08987100232285236</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.171545349039611</v>
+        <v>0.6493988037109375</v>
       </c>
       <c r="BB21" t="n">
-        <v>0.08987100232285236</v>
+        <v>0.0920270284016927</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>7.056532830154524</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0.0920270284016927</v>
       </c>
     </row>
     <row r="22">
@@ -4104,60 +4274,62 @@
           <t>外围\环翠亭方向步行绿道02.jpg</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>0.4057702586484053</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E22" t="n">
-        <v>0.02869462378231096</v>
+        <v>0.4095573425292969</v>
       </c>
       <c r="F22" t="n">
-        <v>0.008683318463863169</v>
+        <v>0.02864201863606771</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1283411724577225</v>
+        <v>0.008413950602213541</v>
       </c>
       <c r="H22" t="n">
-        <v>0.01837208437821502</v>
+        <v>0.1328659057617188</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4160923752438057</v>
+        <v>0.01864878336588542</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3764185507534337</v>
+        <v>0.4160363340689466</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1508566350154899</v>
+        <v>0.3694684346516927</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4389559898847415</v>
+        <v>0.1503618747718627</v>
       </c>
       <c r="M22" t="n">
-        <v>0.04074900434831533</v>
+        <v>0.4405148824055989</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3901117269884903</v>
+        <v>0.04005559285481771</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4431482008945795</v>
+        <v>0.3920796712239583</v>
       </c>
       <c r="P22" t="n">
-        <v>0.0989252412270126</v>
+        <v>0.4466133117675781</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.5457253124360033</v>
+        <v>0.2848904927571614</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4513289938162857</v>
+        <v>0.833061096579317</v>
       </c>
       <c r="S22" t="n">
-        <v>10.77192498269975</v>
+        <v>0.4332149208990955</v>
       </c>
       <c r="T22" t="n">
+        <v>10.99731282693498</v>
+      </c>
+      <c r="U22" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
@@ -4216,25 +4388,25 @@
         <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.02869462378231096</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.008683318463863169</v>
+        <v>0.02864201863606771</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.4057702586484053</v>
+        <v>0.008413950602213541</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.09601589877909594</v>
+        <v>0.4095573425292969</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.01837208437821502</v>
+        <v>0.0987536112467448</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.4579626640665188</v>
+        <v>0.01864878336588542</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>0.4518915812174479</v>
       </c>
       <c r="AV22" t="n">
         <v>0</v>
@@ -4246,16 +4418,22 @@
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.4431482008945795</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.114387983157311</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.874046159542738</v>
+        <v>0.4466133117675781</v>
       </c>
       <c r="BB22" t="n">
-        <v>0.114387983157311</v>
+        <v>0.1174023946126302</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>3.8040919791218</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0.1174023946126302</v>
       </c>
     </row>
     <row r="23">
@@ -4274,59 +4452,61 @@
           <t>外围\环翠亭方向马路01.jpg</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>0.09778698579764661</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E23" t="n">
-        <v>0.281685346438561</v>
+        <v>0.1012827555338542</v>
       </c>
       <c r="F23" t="n">
-        <v>0.007400701075424383</v>
+        <v>0.2812601725260417</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3469724929872364</v>
+        <v>0.007773081461588542</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3567482905132781</v>
+        <v>0.3492749532063802</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4775148924697756</v>
+        <v>0.3675333658854167</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1642410796673431</v>
+        <v>0.4774838615866268</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1319063772112189</v>
+        <v>0.1596540712842754</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0231261704684285</v>
+        <v>0.1313255575935856</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4842580787438915</v>
+        <v>0.02344131469726562</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5322890293451004</v>
+        <v>0.4885546366373698</v>
       </c>
       <c r="O23" t="n">
-        <v>0.386873033311632</v>
+        <v>0.5330563863118489</v>
       </c>
       <c r="P23" t="n">
-        <v>0.05363081315907922</v>
+        <v>0.3903160095214844</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.4889018626771396</v>
+        <v>0.1287930806477865</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5927792639700052</v>
+        <v>0.7267689545963192</v>
       </c>
       <c r="S23" t="n">
-        <v>0.04775578091053025</v>
+        <v>0.5872289235457392</v>
       </c>
       <c r="T23" t="n">
-        <v>0.998992919921875</v>
+        <v>0.04798084995724843</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>0.9999866485595703</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4335,10 +4515,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.001007080078125</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.33514404296875e-05</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -4386,25 +4566,25 @@
         <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.281685346438561</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.007400701075424383</v>
+        <v>0.2812601725260417</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.09778698579764661</v>
+        <v>0.007773081461588542</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.3231664586950231</v>
+        <v>0.1012827555338542</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.3567482905132781</v>
+        <v>0.3246510823567708</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.1848185974874614</v>
+        <v>0.3675333658854167</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>0.168999989827474</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
@@ -4413,19 +4593,25 @@
         <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.001007080078125</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.386873033311632</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.6799147492083012</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>0.5690014296066972</v>
+        <v>0.3903160095214844</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.6799147492083012</v>
+        <v>0.6921844482421875</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0.5638893601601943</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0.6921844482421875</v>
       </c>
     </row>
     <row r="24">
@@ -4444,59 +4630,61 @@
           <t>外围\环翠亭方向马路02.jpg</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>0.1093838538652585</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E24" t="n">
-        <v>0.2534321600517618</v>
+        <v>0.1144383748372396</v>
       </c>
       <c r="F24" t="n">
-        <v>0.006389099874614198</v>
+        <v>0.2532501220703125</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3658079296473122</v>
+        <v>0.007007598876953125</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3583485795637217</v>
+        <v>0.3722254435221354</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4973195989801608</v>
+        <v>0.3680661519368489</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1849354768813229</v>
+        <v>0.4972903332679101</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2332481304549367</v>
+        <v>0.1792163823944291</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1465218626422647</v>
+        <v>0.2327025307472064</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3401862878367734</v>
+        <v>0.1464945475260417</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5469215550049833</v>
+        <v>0.3400853474934896</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3692051137916346</v>
+        <v>0.5497975667317709</v>
       </c>
       <c r="P24" t="n">
-        <v>0.07999015148775077</v>
+        <v>0.3746960957845052</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.4798141601132392</v>
+        <v>0.1726862589518229</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5754381805150296</v>
+        <v>0.7369414266188564</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4307094000307498</v>
+        <v>0.5692230446988567</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9997749328613281</v>
+        <v>0.430756919840324</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>0.9999885559082031</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -4550,34 +4738,34 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.000225067138671875</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.1444091796875e-05</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.2534321600517618</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.006389099874614198</v>
+        <v>0.2532501220703125</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.1093838538652585</v>
+        <v>0.007007598876953125</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.3511223812652713</v>
+        <v>0.1144383748372396</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.3583485795637217</v>
+        <v>0.3581530253092448</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.1871522503134645</v>
+        <v>0.3680661519368489</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.000225067138671875</v>
+        <v>0.1779314676920573</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.1444091796875e-05</v>
       </c>
       <c r="AW24" t="n">
         <v>0</v>
@@ -4586,16 +4774,22 @@
         <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.3692051137916346</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.7094709608289931</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.5203942286319975</v>
+        <v>0.3746960957845052</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.709696027967665</v>
+        <v>0.7262191772460938</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0.5159538491554913</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0.7262306213378906</v>
       </c>
     </row>
     <row r="25">
@@ -4614,59 +4808,61 @@
           <t>外围\环翠亭方向马路03.jpg</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>0.3416682741769547</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E25" t="n">
-        <v>0.4571766794463735</v>
+        <v>0.3453114827473958</v>
       </c>
       <c r="F25" t="n">
-        <v>0.00783165197804141</v>
+        <v>0.4560979207356771</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1571349469722544</v>
+        <v>0.007897694905598959</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00651135856722608</v>
+        <v>0.1564661661783854</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5735490747084102</v>
+        <v>0.007016499837239583</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2685106432448478</v>
+        <v>0.5735266591988358</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1556677851779452</v>
+        <v>0.2647519230063445</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06020848152568802</v>
+        <v>0.1555410494836855</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3452119552549511</v>
+        <v>0.06063969930013021</v>
       </c>
       <c r="N25" t="n">
-        <v>0.334511977458687</v>
+        <v>0.3468208312988281</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8066766056013697</v>
+        <v>0.3335978190104167</v>
       </c>
       <c r="P25" t="n">
-        <v>0.04362883391203703</v>
+        <v>0.8093070983886719</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.3550540157787695</v>
+        <v>0.1553599039713542</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5561573657726444</v>
+        <v>0.6484837698542443</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1744096813551568</v>
+        <v>0.553741698501977</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9994087219238281</v>
+        <v>0.1748439510657042</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>0.9999618530273438</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -4675,10 +4871,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.000591278076171875</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>3.814697265625e-05</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4726,25 +4922,25 @@
         <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.4571766794463735</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.00783165197804141</v>
+        <v>0.4560979207356771</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.3416682741769547</v>
+        <v>0.007897694905598959</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.0655364990234375</v>
+        <v>0.3453114827473958</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.00651135856722608</v>
+        <v>0.06664657592773438</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.1293859913515946</v>
+        <v>0.007016499837239583</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>0.1257921854654948</v>
       </c>
       <c r="AV25" t="n">
         <v>0</v>
@@ -4753,19 +4949,25 @@
         <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.000591278076171875</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.8066766056013696</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.07204785759066358</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>11.19624422339074</v>
+        <v>0.8093070983886719</v>
       </c>
       <c r="BB25" t="n">
-        <v>0.07204785759066358</v>
+        <v>0.07366307576497395</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>10.98645560925484</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0.07366307576497395</v>
       </c>
     </row>
     <row r="26">
@@ -4784,60 +4986,62 @@
           <t>桂海村\桂和巷.jpg</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>0.1383155226216885</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E26" t="n">
-        <v>0.01376612784931198</v>
+        <v>0.1395950317382812</v>
       </c>
       <c r="F26" t="n">
-        <v>0.002178364820441101</v>
+        <v>0.01386006673177083</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3642373418611754</v>
+        <v>0.002363840738932292</v>
       </c>
       <c r="H26" t="n">
-        <v>0.08878863299334491</v>
+        <v>0.3856277465820312</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5270295937817562</v>
+        <v>0.08627827962239583</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2057204989652835</v>
+        <v>0.5269738590016084</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2025759602840856</v>
+        <v>0.202204690571704</v>
       </c>
       <c r="L26" t="n">
-        <v>0.498133529851466</v>
+        <v>0.2009266527179396</v>
       </c>
       <c r="M26" t="n">
-        <v>0.05274605456693673</v>
+        <v>0.4997406005859375</v>
       </c>
       <c r="N26" t="n">
-        <v>0.5881260750225051</v>
+        <v>0.05237833658854166</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1542600152914416</v>
+        <v>0.6006856282552083</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1101938255529835</v>
+        <v>0.1558189392089844</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.5952925642326878</v>
+        <v>0.2585461934407552</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4910201693488859</v>
+        <v>0.8485802795910017</v>
       </c>
       <c r="S26" t="n">
-        <v>9.443816985445658</v>
+        <v>0.4686562524502347</v>
       </c>
       <c r="T26" t="n">
+        <v>9.540796679262623</v>
+      </c>
+      <c r="U26" t="n">
         <v>1</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
@@ -4896,25 +5100,25 @@
         <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>0.01376612784931198</v>
+        <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.002178364820441101</v>
+        <v>0.01386006673177083</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.1383155226216885</v>
+        <v>0.002363840738932292</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.3429652712472672</v>
+        <v>0.1395950317382812</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.08878863299334491</v>
+        <v>0.3635164896647136</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.4689255702642747</v>
+        <v>0.08627827962239583</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>0.447296142578125</v>
       </c>
       <c r="AV26" t="n">
         <v>0</v>
@@ -4926,16 +5130,22 @@
         <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.1542600152914416</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.4317539042406121</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.3572860754477366</v>
+        <v>0.1558189392089844</v>
       </c>
       <c r="BB26" t="n">
-        <v>0.4317539042406121</v>
+        <v>0.4497947692871094</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0.3464215313895572</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0.4497947692871094</v>
       </c>
     </row>
     <row r="27">
@@ -4954,60 +5164,62 @@
           <t>桂海村\桂和路01.jpg</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>0.06209805963461291</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E27" t="n">
-        <v>0.2336628603837127</v>
+        <v>0.0714251200358073</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0239861256791731</v>
+        <v>0.2329050699869792</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3274958732196824</v>
+        <v>0.0258026123046875</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1258046342512217</v>
+        <v>0.3506673177083333</v>
       </c>
       <c r="I27" t="n">
-        <v>0.562497136868548</v>
+        <v>0.09188588460286458</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1644170811127627</v>
+        <v>0.5624568266027113</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2397985009154773</v>
+        <v>0.1542043947706035</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2070013603555813</v>
+        <v>0.2380081314593155</v>
       </c>
       <c r="M27" t="n">
-        <v>0.280444235468107</v>
+        <v>0.2053082784016927</v>
       </c>
       <c r="N27" t="n">
-        <v>0.5373453399281443</v>
+        <v>0.2810134887695312</v>
       </c>
       <c r="O27" t="n">
-        <v>0.3197470456974987</v>
+        <v>0.5495343526204427</v>
       </c>
       <c r="P27" t="n">
-        <v>0.2105022791481803</v>
+        <v>0.3301328023274739</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.671357276615919</v>
+        <v>0.2249704996744792</v>
       </c>
       <c r="R27" t="n">
-        <v>0.5596521607620976</v>
+        <v>0.7969658566375784</v>
       </c>
       <c r="S27" t="n">
-        <v>0.7381168733712435</v>
+        <v>0.5386962226771543</v>
       </c>
       <c r="T27" t="n">
+        <v>0.7305967720763055</v>
+      </c>
+      <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
@@ -5066,25 +5278,25 @@
         <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.2336628603837127</v>
+        <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.0239861256791731</v>
+        <v>0.2329050699869792</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.06209805963461291</v>
+        <v>0.0258026123046875</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.3085043950335969</v>
+        <v>0.0714251200358073</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.1258046342512217</v>
+        <v>0.3307673136393229</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.3298050366311407</v>
+        <v>0.09188588460286458</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>0.3106867472330729</v>
       </c>
       <c r="AV27" t="n">
         <v>0</v>
@@ -5096,16 +5308,22 @@
         <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.3197470456974987</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.4343090292848186</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.7362184249441083</v>
+        <v>0.3301328023274739</v>
       </c>
       <c r="BB27" t="n">
-        <v>0.4343090292848186</v>
+        <v>0.4226531982421875</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0.7810943407175213</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0.4226531982421875</v>
       </c>
     </row>
     <row r="28">
@@ -5124,59 +5342,61 @@
           <t>桂海村\桂和路02.jpg</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>0.1068368291658629</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E28" t="n">
-        <v>0.3630710805885095</v>
+        <v>0.1076787312825521</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01420806759178884</v>
+        <v>0.3629506429036458</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3611759766629694</v>
+        <v>0.01515452067057292</v>
       </c>
       <c r="H28" t="n">
-        <v>0.04049714013872814</v>
+        <v>0.3647664388020833</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6340569385266003</v>
+        <v>0.04109954833984375</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2000179943637853</v>
+        <v>0.6340006660012638</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2230312826179196</v>
+        <v>0.1973726659039267</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2491549268180941</v>
+        <v>0.2229591615631334</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3957193633656443</v>
+        <v>0.2497202555338542</v>
       </c>
       <c r="N28" t="n">
-        <v>0.5227240040469071</v>
+        <v>0.3958854675292969</v>
       </c>
       <c r="O28" t="n">
-        <v>0.4841159773461612</v>
+        <v>0.5247339884440104</v>
       </c>
       <c r="P28" t="n">
-        <v>0.04979175206565072</v>
+        <v>0.4857838948567708</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.4374459350801011</v>
+        <v>0.1473579406738281</v>
       </c>
       <c r="R28" t="n">
-        <v>0.5112787024025602</v>
+        <v>0.6967129568914762</v>
       </c>
       <c r="S28" t="n">
-        <v>0.629623718878161</v>
+        <v>0.5064877409087787</v>
       </c>
       <c r="T28" t="n">
-        <v>0.999603271484375</v>
+        <v>0.6307875515228973</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5221,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.000396728515625</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -5236,46 +5456,52 @@
         <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>0.3630710805885095</v>
+        <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.01420806759178884</v>
+        <v>0.3629506429036458</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.1068368291658629</v>
+        <v>0.01515452067057292</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.3513207455230838</v>
+        <v>0.1076787312825521</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.04049714013872814</v>
+        <v>0.3543968200683594</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.1608054706589185</v>
+        <v>0.04109954833984375</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>0.1563555399576823</v>
       </c>
       <c r="AV28" t="n">
         <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.000396728515625</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
         <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.4841159773461612</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.391817885661812</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.23556059971038</v>
+        <v>0.4857838948567708</v>
       </c>
       <c r="BB28" t="n">
-        <v>0.391817885661812</v>
+        <v>0.3954963684082031</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.228286035914607</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0.3954963684082031</v>
       </c>
     </row>
     <row r="29">
@@ -5294,59 +5520,61 @@
           <t>桂海村\桂和路03.jpg</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>0.1966058550548161</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E29" t="n">
-        <v>0.2803707672244727</v>
+        <v>0.1994921366373698</v>
       </c>
       <c r="F29" t="n">
-        <v>0.05303345982429913</v>
+        <v>0.2799708048502604</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3612250810788001</v>
+        <v>0.05389785766601562</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1837343443568351</v>
+        <v>0.3631324768066406</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5391379618715896</v>
+        <v>0.1872126261393229</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2311199652718678</v>
+        <v>0.5390785915399688</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1936405963966383</v>
+        <v>0.2268253999597886</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1084499280639146</v>
+        <v>0.1934542915843268</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4335047090004501</v>
+        <v>0.1089998881022135</v>
       </c>
       <c r="N29" t="n">
-        <v>0.5213397241914224</v>
+        <v>0.4342765808105469</v>
       </c>
       <c r="O29" t="n">
-        <v>0.530010082103588</v>
+        <v>0.5219868977864583</v>
       </c>
       <c r="P29" t="n">
-        <v>0.04864947786056456</v>
+        <v>0.5333607991536459</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.4432898385528088</v>
+        <v>0.1213061014811198</v>
       </c>
       <c r="R29" t="n">
-        <v>0.5133174131210316</v>
+        <v>0.6931522987150294</v>
       </c>
       <c r="S29" t="n">
-        <v>0.2501695498173981</v>
+        <v>0.5088036158064186</v>
       </c>
       <c r="T29" t="n">
-        <v>0.9997367858886719</v>
+        <v>0.2509912851102591</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>0.9465045928955078</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -5355,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.000263214111328125</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>0.05349540710449219</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -5406,25 +5634,25 @@
         <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.2803707672244727</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.05303345982429913</v>
+        <v>0.2799708048502604</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.1966058550548161</v>
+        <v>0.05389785766601562</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.3041305855959041</v>
+        <v>0.1994921366373698</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.1837343443568351</v>
+        <v>0.3062502543131511</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.1596773877555941</v>
+        <v>0.1872126261393229</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>0.1539891560872396</v>
       </c>
       <c r="AV29" t="n">
         <v>0</v>
@@ -5433,19 +5661,25 @@
         <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.000263214111328125</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.5300100821035879</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.4878649299527392</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.086384700310865</v>
+        <v>0.5333607991536459</v>
       </c>
       <c r="BB29" t="n">
-        <v>0.4878649299527392</v>
+        <v>0.493462880452474</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.080850737574935</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0.493462880452474</v>
       </c>
     </row>
     <row r="30">
@@ -5464,59 +5698,61 @@
           <t>桂海村\桂海村广场.jpg</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>0.2309089315280993</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E30" t="n">
-        <v>0.1554824138374486</v>
+        <v>0.235565185546875</v>
       </c>
       <c r="F30" t="n">
-        <v>0.04385903440875771</v>
+        <v>0.1552047729492188</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2725416897746271</v>
+        <v>0.04719416300455729</v>
       </c>
       <c r="H30" t="n">
-        <v>0.05387470261059671</v>
+        <v>0.2810490926106771</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4749427400796916</v>
+        <v>0.05629857381184896</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2559153913653215</v>
+        <v>0.4748804578594133</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2475879153280965</v>
+        <v>0.2502950182148054</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3195235640914352</v>
+        <v>0.2469717512703802</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2171630231441294</v>
+        <v>0.3175900777180989</v>
       </c>
       <c r="N30" t="n">
-        <v>0.4862467447916667</v>
+        <v>0.217278798421224</v>
       </c>
       <c r="O30" t="n">
-        <v>0.4302503797743056</v>
+        <v>0.4904754638671875</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0747785528991448</v>
+        <v>0.437964121500651</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.5282681082460474</v>
+        <v>0.1864306131998698</v>
       </c>
       <c r="R30" t="n">
-        <v>0.4795604098340476</v>
+        <v>0.7851093301152605</v>
       </c>
       <c r="S30" t="n">
-        <v>1.47134667826342</v>
+        <v>0.4659350116600032</v>
       </c>
       <c r="T30" t="n">
-        <v>0.9996738433837891</v>
+        <v>1.461664084860807</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>0.9999141693115234</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -5558,10 +5794,10 @@
         <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.0003261566162109375</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>8.58306884765625e-05</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -5576,46 +5812,52 @@
         <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.1554824138374486</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.04385903440875771</v>
+        <v>0.1552047729492188</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.2309089315280993</v>
+        <v>0.04719416300455729</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.2374261926721644</v>
+        <v>0.235565185546875</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.05387470261059671</v>
+        <v>0.2469800313313802</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.3333155628094457</v>
+        <v>0.05629857381184896</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>0.3173014322916667</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.0003261566162109375</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>8.58306884765625e-05</v>
       </c>
       <c r="AX30" t="n">
         <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.4302503797743056</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.291300895282761</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.476991350697084</v>
+        <v>0.4379641215006511</v>
       </c>
       <c r="BB30" t="n">
-        <v>0.291627051898972</v>
+        <v>0.3032786051432292</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.444093549560693</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0.3033644358317057</v>
       </c>
     </row>
     <row r="31">
@@ -5634,59 +5876,61 @@
           <t>桂海村\桂海村村口01.jpg</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>0.04347203886557999</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E31" t="n">
-        <v>0.3969788100003215</v>
+        <v>0.044036865234375</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01524955843701775</v>
+        <v>0.3912340799967448</v>
       </c>
       <c r="G31" t="n">
-        <v>0.305550092532311</v>
+        <v>0.01678212483723958</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2908752190232767</v>
+        <v>0.3194986979166667</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5527301323843822</v>
+        <v>0.300811767578125</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1627731056062552</v>
+        <v>0.5526761372884115</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1793261756197891</v>
+        <v>0.1589529049941917</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1002972135818544</v>
+        <v>0.178699669810327</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5873259870113169</v>
+        <v>0.1009648640950521</v>
       </c>
       <c r="N31" t="n">
-        <v>0.4952398857462063</v>
+        <v>0.5896453857421875</v>
       </c>
       <c r="O31" t="n">
-        <v>0.4557004073029192</v>
+        <v>0.5046450297037761</v>
       </c>
       <c r="P31" t="n">
-        <v>0.04557875645013503</v>
+        <v>0.4520530700683594</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.5077513820920365</v>
+        <v>0.094818115234375</v>
       </c>
       <c r="R31" t="n">
-        <v>0.6592148305024772</v>
+        <v>0.72988949427298</v>
       </c>
       <c r="S31" t="n">
-        <v>0.1707689511974049</v>
+        <v>0.6532053758908637</v>
       </c>
       <c r="T31" t="n">
-        <v>0.9913291931152344</v>
+        <v>0.1712295140552209</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>0.9899806976318359</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -5695,10 +5939,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.008670806884765625</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>0.01001930236816406</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -5746,25 +5990,25 @@
         <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>0.3969788100003215</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.01524955843701775</v>
+        <v>0.3912340799967448</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.04347203886557999</v>
+        <v>0.01678212483723958</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.2669512587810249</v>
+        <v>0.044036865234375</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.2908752190232767</v>
+        <v>0.2816632588704427</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.1789607295283565</v>
+        <v>0.300811767578125</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>0.1645685831705729</v>
       </c>
       <c r="AV31" t="n">
         <v>0</v>
@@ -5773,19 +6017,25 @@
         <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.008670806884765625</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.4557004073029192</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.5578264778043016</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.8169199715593592</v>
+        <v>0.4520530700683594</v>
       </c>
       <c r="BB31" t="n">
-        <v>0.5578264778043016</v>
+        <v>0.5824750264485676</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0.7760887135983706</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0.5824750264485676</v>
       </c>
     </row>
     <row r="32">
@@ -5804,68 +6054,70 @@
           <t>桂海村\桂海村村口02.jpg</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>0.04028370547196502</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E32" t="n">
-        <v>0.09359201187950103</v>
+        <v>0.04369227091471354</v>
       </c>
       <c r="F32" t="n">
-        <v>0.02315461586532279</v>
+        <v>0.09526952107747395</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4094139067724408</v>
+        <v>0.02479680379231771</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3328107041096001</v>
+        <v>0.432281494140625</v>
       </c>
       <c r="I32" t="n">
-        <v>0.453250130442762</v>
+        <v>0.3388188680013021</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1552852877171557</v>
+        <v>0.4531798269234452</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2550731187909581</v>
+        <v>0.1499232622533063</v>
       </c>
       <c r="L32" t="n">
-        <v>0.228586769888921</v>
+        <v>0.2532144084277148</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2152617026748971</v>
+        <v>0.2272313435872396</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6188732005931713</v>
+        <v>0.2116813659667969</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1570303332167888</v>
+        <v>0.6315765380859375</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1268682283629115</v>
+        <v>0.1637585957845052</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.6212211766362814</v>
+        <v>0.1771926879882812</v>
       </c>
       <c r="R32" t="n">
-        <v>0.5170209953564576</v>
+        <v>0.8084981593096993</v>
       </c>
       <c r="S32" t="n">
-        <v>1.061896775653452</v>
+        <v>0.4973719966904228</v>
       </c>
       <c r="T32" t="n">
-        <v>0.9839000701904297</v>
+        <v>1.07345428869064</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.9836215972900391</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>5.7220458984375e-06</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.00057220458984375</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -5898,10 +6150,10 @@
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.01609420776367188</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>0.01580619812011719</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -5916,46 +6168,52 @@
         <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.09359201187950103</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.02315461586532279</v>
+        <v>0.09526952107747395</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.04028370547196502</v>
+        <v>0.02479680379231771</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.386403966833044</v>
+        <v>0.04369227091471354</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.3328107041096001</v>
+        <v>0.4033037821451823</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.357857221438561</v>
+        <v>0.3388188680013021</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>0.336517333984375</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.01609420776367188</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>0.01580619812011719</v>
       </c>
       <c r="AX32" t="n">
         <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.1570303332167888</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.719214670942644</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.2183355279383389</v>
+        <v>0.1637585957845052</v>
       </c>
       <c r="BB32" t="n">
-        <v>0.7353088787063159</v>
+        <v>0.7421226501464844</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0.220662144040527</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0.7579288482666016</v>
       </c>
     </row>
     <row r="33">
@@ -5974,60 +6232,62 @@
           <t>桂海村\桂海村村口03.jpg</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>0.01022577481995885</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E33" t="n">
-        <v>0.07153207284432871</v>
+        <v>0.01034800211588542</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01843764065715021</v>
+        <v>0.06286875406901042</v>
       </c>
       <c r="G33" t="n">
-        <v>0.397607622813786</v>
+        <v>0.01966730753580729</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4536007225758745</v>
+        <v>0.4576937357584636</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3757185248402103</v>
+        <v>0.5152562459309896</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1344756329020163</v>
+        <v>0.3756369347665824</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2548296085880736</v>
+        <v>0.1201681598339205</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1605335753641011</v>
+        <v>0.2526638130482001</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2155250580713091</v>
+        <v>0.1582501729329427</v>
       </c>
       <c r="N33" t="n">
-        <v>0.6222130041554141</v>
+        <v>0.1988512674967448</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1001954883214378</v>
+        <v>0.659972890218099</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1568279501832562</v>
+        <v>0.09288406372070314</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.6996011844263496</v>
+        <v>0.1585845947265625</v>
       </c>
       <c r="R33" t="n">
-        <v>0.4762492423732786</v>
+        <v>0.8149035565999494</v>
       </c>
       <c r="S33" t="n">
-        <v>0.7448453184764637</v>
+        <v>0.4473321984674499</v>
       </c>
       <c r="T33" t="n">
+        <v>0.7958177944112872</v>
+      </c>
+      <c r="U33" t="n">
         <v>1</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
@@ -6086,25 +6346,25 @@
         <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.07153207284432871</v>
+        <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.01843764065715021</v>
+        <v>0.06286875406901042</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.01022577481995885</v>
+        <v>0.01966730753580729</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.370563146018197</v>
+        <v>0.01034800211588542</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.4536007225758745</v>
+        <v>0.4317105611165364</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.3285359198173868</v>
+        <v>0.5152562459309896</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>0.2782669067382812</v>
       </c>
       <c r="AV33" t="n">
         <v>0</v>
@@ -6116,16 +6376,22 @@
         <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.1001954883214378</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.8241638685940715</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.1215721418608385</v>
+        <v>0.09288406372070314</v>
       </c>
       <c r="BB33" t="n">
-        <v>0.8241638685940715</v>
+        <v>0.9469668070475261</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0.09808576704449838</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0.9469668070475261</v>
       </c>
     </row>
     <row r="34">
@@ -6144,59 +6410,61 @@
           <t>桂海村\海景03.jpg</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>0.1286660653573495</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E34" t="n">
-        <v>0.2986965100951646</v>
+        <v>0.1284014383951823</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1424990053530093</v>
+        <v>0.2984949747721354</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5458534774466307</v>
+        <v>0.1434427897135417</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1224772135416667</v>
+        <v>0.5478680928548177</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5500909166744679</v>
+        <v>0.1239344278971354</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1535193820135516</v>
+        <v>0.55007855783101</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1298310485978656</v>
+        <v>0.1530247756858277</v>
       </c>
       <c r="L34" t="n">
-        <v>0.03374716676311729</v>
+        <v>0.1295045489897362</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4264674559542181</v>
+        <v>0.03393427530924479</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6420395713774756</v>
+        <v>0.4267654418945312</v>
       </c>
       <c r="O34" t="n">
-        <v>0.5698615808055234</v>
+        <v>0.6433415730794271</v>
       </c>
       <c r="P34" t="n">
-        <v>0.01241399819958848</v>
+        <v>0.5703392028808594</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.3107876947027249</v>
+        <v>0.05506388346354166</v>
       </c>
       <c r="R34" t="n">
-        <v>0.4277896209692045</v>
+        <v>0.5657743997896197</v>
       </c>
       <c r="S34" t="n">
-        <v>0.07913168322756346</v>
+        <v>0.4261312503887604</v>
       </c>
       <c r="T34" t="n">
-        <v>0.9999065399169922</v>
+        <v>0.07951486334914573</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>0.99969482421875</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -6205,10 +6473,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>9.34600830078125e-05</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>0.00030517578125</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -6256,25 +6524,25 @@
         <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>0.2986965100951646</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.1424990053530093</v>
+        <v>0.2984949747721354</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.1286660653573495</v>
+        <v>0.1434427897135417</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.2816103711540316</v>
+        <v>0.1284014383951823</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.1224772135416667</v>
+        <v>0.2836596171061198</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.2349695276331019</v>
+        <v>0.1239344278971354</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>0.2328529357910156</v>
       </c>
       <c r="AV34" t="n">
         <v>0</v>
@@ -6283,19 +6551,25 @@
         <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>9.34600830078125e-05</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.5698615808055234</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.4040875846956983</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.410239245522517</v>
+        <v>0.5703392028808594</v>
       </c>
       <c r="BB34" t="n">
-        <v>0.4040875846956983</v>
+        <v>0.4075940450032552</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.399279039018505</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0.4075940450032552</v>
       </c>
     </row>
     <row r="35">
@@ -6314,59 +6588,61 @@
           <t>桂海村\蓝色海岸01.jpg</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>0.1497053609463413</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E35" t="n">
-        <v>0.1422320079411008</v>
+        <v>0.1494356791178385</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02999406979407793</v>
+        <v>0.141546885172526</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3221861913861561</v>
+        <v>0.03119786580403646</v>
       </c>
       <c r="H35" t="n">
-        <v>0.08781357753423998</v>
+        <v>0.3406791687011719</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5368958588249794</v>
+        <v>0.08868789672851562</v>
       </c>
       <c r="J35" t="n">
-        <v>0.223028814395365</v>
+        <v>0.5368321736653646</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2427469038888763</v>
+        <v>0.218762700697955</v>
       </c>
       <c r="L35" t="n">
-        <v>0.3857180120523084</v>
+        <v>0.2419310055592328</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1064659087255658</v>
+        <v>0.3875567118326823</v>
       </c>
       <c r="N35" t="n">
-        <v>0.5349242410542052</v>
+        <v>0.1077079772949219</v>
       </c>
       <c r="O35" t="n">
-        <v>0.3219314386815201</v>
+        <v>0.5462109883626303</v>
       </c>
       <c r="P35" t="n">
-        <v>0.08477663895720808</v>
+        <v>0.322180430094401</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.5594237944360362</v>
+        <v>0.2107378641764323</v>
       </c>
       <c r="R35" t="n">
-        <v>0.5440320778328971</v>
+        <v>0.7972714800529921</v>
       </c>
       <c r="S35" t="n">
-        <v>3.622891062297614</v>
+        <v>0.5307917716340612</v>
       </c>
       <c r="T35" t="n">
-        <v>0.9919548034667969</v>
+        <v>3.5981839356946</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>0.9849376678466797</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -6375,10 +6651,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.004636764526367188</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>0.000354766845703125</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -6390,10 +6666,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.0006198883056640625</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>0.00588226318359375</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -6408,13 +6684,13 @@
         <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.002788543701171875</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>0.00286102294921875</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>0.005964279174804688</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6426,46 +6702,52 @@
         <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>0.1422320079411008</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.02999406979407793</v>
+        <v>0.141546885172526</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.1497053609463413</v>
+        <v>0.03119786580403646</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.2816089896998779</v>
+        <v>0.1494356791178385</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.08781357753423998</v>
+        <v>0.2972450256347656</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.3760315066992991</v>
+        <v>0.08868789672851562</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>0.3612785339355469</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.002788543701171875</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>0.00286102294921875</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.004636764526367188</v>
+        <v>0.005964279174804688</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.3219314386815201</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.3694225672341178</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.8714426128571809</v>
+        <v>0.322180430094401</v>
       </c>
       <c r="BB35" t="n">
-        <v>0.3722111109352897</v>
+        <v>0.3859329223632812</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0.8348072336360502</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0.3887939453125</v>
       </c>
     </row>
     <row r="36">
@@ -6484,59 +6766,61 @@
           <t>桂海村\蓝色海岸02.jpg</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>0.03856900690023791</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E36" t="n">
-        <v>0.08846562389483667</v>
+        <v>0.03975423177083334</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01995535642521862</v>
+        <v>0.0882568359375</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1977147231867284</v>
+        <v>0.02250925699869792</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1222875775623714</v>
+        <v>0.2099520365397135</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4937671440676724</v>
+        <v>0.1284294128417969</v>
       </c>
       <c r="J36" t="n">
-        <v>0.2532021959536129</v>
+        <v>0.4937160317414726</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2733787772589613</v>
+        <v>0.2481203715006511</v>
       </c>
       <c r="L36" t="n">
-        <v>0.4640308898172261</v>
+        <v>0.2714691606060677</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1379642565063979</v>
+        <v>0.4647318522135417</v>
       </c>
       <c r="N36" t="n">
-        <v>0.4932219077530222</v>
+        <v>0.1387952168782552</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1469899872202932</v>
+        <v>0.5003690083821615</v>
       </c>
       <c r="P36" t="n">
-        <v>0.05042219750675155</v>
+        <v>0.1505203247070312</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.5369246977867425</v>
+        <v>0.1475270589192708</v>
       </c>
       <c r="R36" t="n">
-        <v>0.5143532326779683</v>
+        <v>0.7816557959681967</v>
       </c>
       <c r="S36" t="n">
-        <v>3.363389461720802</v>
+        <v>0.5024387554288688</v>
       </c>
       <c r="T36" t="n">
-        <v>0.9918594360351562</v>
+        <v>3.348303452832437</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>0.9893283843994141</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -6581,10 +6865,10 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.00814056396484375</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>0.01067161560058594</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6596,46 +6880,52 @@
         <v>0</v>
       </c>
       <c r="AO36" t="n">
-        <v>0.08846562389483667</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.01995535642521862</v>
+        <v>0.0882568359375</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.03856900690023791</v>
+        <v>0.02250925699869792</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.1849587522907022</v>
+        <v>0.03975423177083334</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.1222875775623714</v>
+        <v>0.1950060526529948</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.605560302734375</v>
+        <v>0.1284294128417969</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>0.5903269449869791</v>
       </c>
       <c r="AV36" t="n">
         <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.00814056396484375</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>0.01067161560058594</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.1469899872202932</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.3072463298530735</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.4784093234938257</v>
+        <v>0.1505203247070312</v>
       </c>
       <c r="BB36" t="n">
-        <v>0.3072463298530735</v>
+        <v>0.3234354654947916</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0.4653783378344985</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0.3234354654947916</v>
       </c>
     </row>
     <row r="37">
@@ -6654,59 +6944,61 @@
           <t>桂海村\长梯巷.jpg</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>0.03983485845871913</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>coco</t>
+        </is>
       </c>
       <c r="E37" t="n">
-        <v>0.1108805338541667</v>
+        <v>0.0417022705078125</v>
       </c>
       <c r="F37" t="n">
-        <v>0.03999159071180555</v>
+        <v>0.1106478373209635</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2482668401773084</v>
+        <v>0.0423431396484375</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1607740739736047</v>
+        <v>0.2557271321614583</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3356367532444916</v>
+        <v>0.1665318806966146</v>
       </c>
       <c r="J37" t="n">
-        <v>0.2746546480352284</v>
+        <v>0.3355804692685994</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2927936220689901</v>
+        <v>0.2662553026785259</v>
       </c>
       <c r="L37" t="n">
-        <v>0.400142277219168</v>
+        <v>0.2912575817824392</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2077767956894612</v>
+        <v>0.4002774556477864</v>
       </c>
       <c r="N37" t="n">
-        <v>0.5188170256438079</v>
+        <v>0.2080497741699219</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1907069830246914</v>
+        <v>0.5229662577311198</v>
       </c>
       <c r="P37" t="n">
-        <v>0.04964638541264789</v>
+        <v>0.1946932474772136</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.5315342064972991</v>
+        <v>0.1560249328613281</v>
       </c>
       <c r="R37" t="n">
-        <v>0.4967862348531626</v>
+        <v>0.7642500846455506</v>
       </c>
       <c r="S37" t="n">
-        <v>1.925818280492345</v>
+        <v>0.4858016125930594</v>
       </c>
       <c r="T37" t="n">
-        <v>0.9999504089355469</v>
+        <v>1.923941197742753</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -6751,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>4.9591064453125e-05</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
         <v>0</v>
@@ -6766,46 +7058,52 @@
         <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>0.1108805338541667</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.03999159071180555</v>
+        <v>0.1106478373209635</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.03983485845871913</v>
+        <v>0.0423431396484375</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.2160901356135867</v>
+        <v>0.0417022705078125</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.1607740739736047</v>
+        <v>0.2221946716308594</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.5356428358289931</v>
+        <v>0.1665318806966146</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>0.5240681966145834</v>
       </c>
       <c r="AV37" t="n">
         <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.9591064453125e-05</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
         <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.1907069830246914</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.3768642095871914</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.5060349912203013</v>
+        <v>0.1946932474772136</v>
       </c>
       <c r="BB37" t="n">
-        <v>0.3768642095871914</v>
+        <v>0.388726552327474</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0.5008475635737778</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0.388726552327474</v>
       </c>
     </row>
   </sheetData>
